--- a/data/trans_dic/P36B13_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36B13_R-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,47</t>
+          <t>4,19; 9,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,25</t>
+          <t>3,28; 7,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,11</t>
+          <t>2,75; 7,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,38</t>
+          <t>1,47; 4,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,19</t>
+          <t>3,9; 7,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,05</t>
+          <t>2,77; 5,34</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,67</t>
+          <t>6,47; 12,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,27</t>
+          <t>3,46; 9,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 11,06</t>
+          <t>5,77; 11,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,0</t>
+          <t>3,1; 7,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,03</t>
+          <t>6,74; 10,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,48</t>
+          <t>3,68; 7,36</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 13,68</t>
+          <t>8,1; 13,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 75,93</t>
+          <t>4,77; 10,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,41</t>
+          <t>4,91; 14,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,8</t>
+          <t>0,8; 4,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 12,71</t>
+          <t>7,84; 12,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 65,33</t>
+          <t>4,07; 8,42</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,51</t>
+          <t>10,53; 14,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,21</t>
+          <t>6,97; 10,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,52</t>
+          <t>9,19; 13,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,16</t>
+          <t>3,27; 6,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 13,42</t>
+          <t>10,54; 13,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,79</t>
+          <t>5,79; 8,43</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 18,02</t>
+          <t>12,21; 18,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,51</t>
+          <t>4,87; 10,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,49</t>
+          <t>5,5; 9,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,89</t>
+          <t>2,2; 4,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,2; 12,6</t>
+          <t>9,12; 12,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,48</t>
+          <t>3,59; 5,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,61; 28,54</t>
+          <t>18,47; 28,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 18,39</t>
+          <t>5,52; 19,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,98</t>
+          <t>4,85; 8,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,35</t>
+          <t>2,97; 6,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,75</t>
+          <t>8,5; 11,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,07</t>
+          <t>4,53; 8,22</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,39; 13,56</t>
+          <t>11,33; 13,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 38,27</t>
+          <t>6,33; 8,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,81</t>
+          <t>6,98; 8,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,2</t>
+          <t>3,27; 4,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,44; 10,87</t>
+          <t>9,35; 10,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 20,18</t>
+          <t>5,01; 6,23</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>40460</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17482; 36182</t>
+          <t>17883; 38426</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15928; 36625</t>
+          <t>18036; 41606</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9551; 24504</t>
+          <t>9478; 24315</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6515; 19510</t>
+          <t>7152; 19787</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30816; 55491</t>
+          <t>30082; 55807</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25922; 48013</t>
+          <t>28750; 55427</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44442</t>
+          <t>47339</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24225; 47294</t>
+          <t>24168; 46774</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15821; 41917</t>
+          <t>16698; 44981</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20804; 40803</t>
+          <t>21303; 42520</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11760; 30477</t>
+          <t>13052; 30750</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49653; 81868</t>
+          <t>50031; 81210</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31298; 62306</t>
+          <t>33309; 66549</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>271822</t>
+          <t>33803</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>275732</t>
+          <t>38147</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42250; 70752</t>
+          <t>41882; 70114</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36987; 505370</t>
+          <t>22348; 49715</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8805; 23819</t>
+          <t>8120; 23723</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1393; 8009</t>
+          <t>1495; 8827</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55414; 86715</t>
+          <t>53502; 87641</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39612; 543873</t>
+          <t>26723; 55264</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>99466</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>38235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>125592</t>
+          <t>137702</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121924; 166174</t>
+          <t>120666; 166412</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70966; 115977</t>
+          <t>78855; 123159</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75194; 111262</t>
+          <t>75625; 111276</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16597; 50307</t>
+          <t>28044; 52429</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>207970; 264177</t>
+          <t>207509; 266950</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86072; 156534</t>
+          <t>115230; 167861</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>39434</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>65841</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>76283; 110824</t>
+          <t>75071; 111938</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20848; 45031</t>
+          <t>27567; 56732</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40397; 69832</t>
+          <t>40448; 70766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14428; 32654</t>
+          <t>18266; 35567</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>124270; 170227</t>
+          <t>123268; 170486</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41615; 72010</t>
+          <t>50143; 82415</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>27772</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57373</t>
+          <t>65740</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53442; 81964</t>
+          <t>53034; 82153</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12056; 44219</t>
+          <t>13105; 45977</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52891; 85403</t>
+          <t>51896; 85772</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21406; 48185</t>
+          <t>24994; 53042</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>114930; 159515</t>
+          <t>115382; 159708</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41728; 80712</t>
+          <t>48919; 88726</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>469296</t>
+          <t>255947</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123866</t>
+          <t>139281</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>593162</t>
+          <t>395228</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>383408; 456218</t>
+          <t>381180; 457418</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>228799; 1290304</t>
+          <t>217759; 296938</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>244609; 308936</t>
+          <t>245022; 306987</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>98381; 149959</t>
+          <t>118494; 165458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>648716; 747410</t>
+          <t>642317; 746295</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>346455; 1400690</t>
+          <t>354089; 440369</t>
         </is>
       </c>
     </row>
